--- a/3_datawarehouse/Data dictionary.xlsx
+++ b/3_datawarehouse/Data dictionary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tioua\Desktop\football-analytics-bigdata\3_datawarehouse\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FDD7BF5-9321-4739-8416-F61F1AB2DFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04915EF2-C22B-4E1F-A328-69F60A3E5603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-3480" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{1B36BA4D-4460-47C9-9AD4-F25ECDE36BE6}"/>
   </bookViews>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
   <si>
     <t>Clé / FK</t>
   </si>
   <si>
-    <t>Mesures</t>
-  </si>
-  <si>
     <t>match_id (PK)</t>
   </si>
   <si>
@@ -125,9 +122,6 @@
     <t>Clé</t>
   </si>
   <si>
-    <t>Attribut</t>
-  </si>
-  <si>
     <t>team_id (PK)</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>Nom arbitre</t>
   </si>
   <si>
-    <t>Attributs</t>
-  </si>
-  <si>
     <t>date_id (PK)</t>
   </si>
   <si>
@@ -228,6 +219,21 @@
   </si>
   <si>
     <t>Dimensions : Dim_Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Ville de l’équipe</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>Pays de l’équipe</t>
   </si>
 </sst>
 </file>
@@ -288,6 +294,15 @@
   </cellStyles>
   <dxfs count="20">
     <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -418,15 +433,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -441,55 +447,55 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6F6B2B79-7D25-4E48-8989-B92F55090DE7}" name="Table2" displayName="Table2" ref="A38:B45" totalsRowShown="0" headerRowDxfId="16" dataDxfId="17">
-  <autoFilter ref="A38:B45" xr:uid="{6F6B2B79-7D25-4E48-8989-B92F55090DE7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6F6B2B79-7D25-4E48-8989-B92F55090DE7}" name="Table2" displayName="Table2" ref="A41:B48" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A41:B48" xr:uid="{6F6B2B79-7D25-4E48-8989-B92F55090DE7}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A1EF8F17-64A7-4FEF-B3DB-482EDEEA28C1}" name="Clé" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{B4B38541-36CC-476B-8F53-714F017E0C08}" name="Attributs" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{A1EF8F17-64A7-4FEF-B3DB-482EDEEA28C1}" name="Clé" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{B4B38541-36CC-476B-8F53-714F017E0C08}" name="Description" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2F5D4F71-A8AA-4CB1-8BD5-EEC987CD03FB}" name="Table3" displayName="Table3" ref="A2:B15" totalsRowShown="0" headerRowDxfId="12" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{2F5D4F71-A8AA-4CB1-8BD5-EEC987CD03FB}" name="Table3" displayName="Table3" ref="A2:B15" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A2:B15" xr:uid="{2F5D4F71-A8AA-4CB1-8BD5-EEC987CD03FB}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{9BC81B74-6731-4CF3-B235-C24C8C43FB38}" name="Clé / FK" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{61512049-1A67-4E83-8707-5CC959564DFC}" name="Mesures" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{9BC81B74-6731-4CF3-B235-C24C8C43FB38}" name="Clé / FK" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{61512049-1A67-4E83-8707-5CC959564DFC}" name="Description" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2447D355-FAAA-416B-9584-90B9D72B5816}" name="Table4" displayName="Table4" ref="A18:B20" totalsRowShown="0" headerRowDxfId="8" dataDxfId="9">
-  <autoFilter ref="A18:B20" xr:uid="{2447D355-FAAA-416B-9584-90B9D72B5816}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2447D355-FAAA-416B-9584-90B9D72B5816}" name="Table4" displayName="Table4" ref="A18:B22" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A18:B22" xr:uid="{2447D355-FAAA-416B-9584-90B9D72B5816}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{C851CE4F-E592-41D0-B09B-4750A4F1B4AF}" name="Clé" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{470A12F2-7120-4F5A-8BBF-41214AD54C31}" name="Attribut" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{C851CE4F-E592-41D0-B09B-4750A4F1B4AF}" name="Clé" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{470A12F2-7120-4F5A-8BBF-41214AD54C31}" name="Description" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A61C5CCD-942F-4C47-ACD7-ED8D8C961A87}" name="Table5" displayName="Table5" ref="A24:B27" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5">
-  <autoFilter ref="A24:B27" xr:uid="{A61C5CCD-942F-4C47-ACD7-ED8D8C961A87}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{A61C5CCD-942F-4C47-ACD7-ED8D8C961A87}" name="Table5" displayName="Table5" ref="A26:B29" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A26:B29" xr:uid="{A61C5CCD-942F-4C47-ACD7-ED8D8C961A87}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E803B1CF-AFBB-4205-883C-B95C1A59E6FF}" name="Clé" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{F13CBD45-9890-4BDB-89DF-4E86C71B5FF8}" name="Attribut" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{E803B1CF-AFBB-4205-883C-B95C1A59E6FF}" name="Clé" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{F13CBD45-9890-4BDB-89DF-4E86C71B5FF8}" name="Description" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2F718043-DE83-400C-BC24-AD132648C389}" name="Table6" displayName="Table6" ref="A31:B33" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A31:B33" xr:uid="{2F718043-DE83-400C-BC24-AD132648C389}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2F718043-DE83-400C-BC24-AD132648C389}" name="Table6" displayName="Table6" ref="A34:B36" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A34:B36" xr:uid="{2F718043-DE83-400C-BC24-AD132648C389}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{54017F25-2B95-4F46-8DDF-F24BB5B3E871}" name="Clé" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{280C51A1-FC62-47E8-B8F4-4911CD3A1786}" name="Attribut" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{54017F25-2B95-4F46-8DDF-F24BB5B3E871}" name="Clé" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{280C51A1-FC62-47E8-B8F4-4911CD3A1786}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -812,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A4A229-EC9A-42F8-9428-E0E80CE96193}">
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -821,7 +827,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3"/>
     </row>
@@ -830,288 +836,304 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B23" s="3"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B33" s="3"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B36" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B37" s="3"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A40" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="3"/>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>50</v>
+      <c r="A41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
